--- a/output/2026-09-20_19_Croazia_Istarska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-20_19_Croazia_Istarska_Impiantistica_aspirazione_industriale.xlsx
@@ -474,7 +474,6 @@
           <t>MYS d.o.o.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Istarska (Pula)</t>
@@ -502,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -532,7 +531,6 @@
           <t>052 851 846 / 052 853 548 (fax) / 098 420 544</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Impianti di riscaldamento, climatizzazione, ventilazione e sistemi solari (installatore B2B). Attiva dal 1993. Attivita' prevalentemente HVAC generalista, non specializzata in aspirazione industriale in senso stretto - pertinenza da confermare in fase commerciale.</t>
@@ -550,7 +548,6 @@
           <t>ZENO d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Istarska (Pula)</t>
@@ -566,7 +563,6 @@
           <t>052 545 245</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Progettazione impianti (riscaldamento centralizzato, ventilazione/recupero aria) - studio di progettazione/installatore B2B. Presente in directory settoriali (emajstor.hr, eistra.info).</t>
@@ -604,7 +600,6 @@
           <t>052 663 181</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Ditta individuale (obrt) attiva dal 1994. Installazione impianti di ventilazione/climatizzazione, canne fumarie inox, cappe, filtri, lavorazione lamiera CNC. Buon fit col settore (cappe, filtri).</t>
@@ -612,7 +607,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -684,7 +679,6 @@
           <t>+385 99 244 7915 / +385 52 556 866</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Progettazione impianti meccanici (riscaldamento, raffrescamento, ventilazione, idraulica, gas) e sistemi tecnologici/di processo per edifici residenziali, commerciali e industriali. Attiva dal 2011, studio di progettazione/system integrator B2B.</t>
